--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.66239048636419</v>
+        <v>5.632638454034181</v>
       </c>
       <c r="D2" t="n">
-        <v>24.41558902943611</v>
+        <v>3.967533217283368</v>
       </c>
       <c r="E2" t="n">
-        <v>12.18050900178409</v>
+        <v>1.979332712789915</v>
       </c>
       <c r="F2" t="n">
-        <v>8.009631602539674</v>
+        <v>1.301565135412697</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.98565063197095</v>
+        <v>2.922668227695279</v>
       </c>
       <c r="D3" t="n">
-        <v>17.60829702088744</v>
+        <v>2.861348265894209</v>
       </c>
       <c r="E3" t="n">
-        <v>12.18050900178409</v>
+        <v>1.979332712789915</v>
       </c>
       <c r="F3" t="n">
-        <v>8.009631602539674</v>
+        <v>1.301565135412697</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.898420011852354</v>
+        <v>0.7959932519260077</v>
       </c>
       <c r="D4" t="n">
-        <v>5.076464542525236</v>
+        <v>0.8249254881603508</v>
       </c>
       <c r="E4" t="n">
-        <v>12.18050900178409</v>
+        <v>1.979332712789915</v>
       </c>
       <c r="F4" t="n">
-        <v>8.009631602539674</v>
+        <v>1.301565135412697</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
